--- a/config/测控柜_鸿合.xlsx
+++ b/config/测控柜_鸿合.xlsx
@@ -934,7 +934,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -944,13 +944,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1405,28 +1398,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1435,118 +1431,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/config/测控柜_鸿合.xlsx
+++ b/config/测控柜_鸿合.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="296">
   <si>
     <t>序号</t>
   </si>
@@ -436,9 +436,6 @@
   </si>
   <si>
     <t>AA3柜温湿度控制器</t>
-  </si>
-  <si>
-    <t>AA4柜温湿度控制器</t>
   </si>
   <si>
     <t>A相绕组温度</t>
@@ -1894,7 +1891,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="16.034188034188" customWidth="1"/>
@@ -5396,7 +5393,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>16493</v>
@@ -5411,16 +5408,16 @@
         <v>117</v>
       </c>
       <c r="G110" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
       </c>
       <c r="I110" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="J110" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -5428,7 +5425,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C111">
         <v>16494</v>
@@ -5440,19 +5437,19 @@
         <v>0</v>
       </c>
       <c r="F111" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G111" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
       </c>
       <c r="I111" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="J111" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -5460,7 +5457,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C112">
         <v>16495</v>
@@ -5475,16 +5472,16 @@
         <v>117</v>
       </c>
       <c r="G112" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
       </c>
       <c r="I112" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="J112" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -5492,7 +5489,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C113">
         <v>16496</v>
@@ -5504,19 +5501,19 @@
         <v>0</v>
       </c>
       <c r="F113" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G113" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H113" t="s">
         <v>13</v>
       </c>
       <c r="I113" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J113" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -5524,7 +5521,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C114">
         <v>16497</v>
@@ -5539,144 +5536,16 @@
         <v>117</v>
       </c>
       <c r="G114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H114" t="s">
         <v>13</v>
       </c>
       <c r="I114" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J114" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" t="s">
-        <v>140</v>
-      </c>
-      <c r="C115">
-        <v>16498</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115" t="s">
-        <v>117</v>
-      </c>
-      <c r="G115" t="s">
-        <v>137</v>
-      </c>
-      <c r="H115" t="s">
-        <v>13</v>
-      </c>
-      <c r="I115" t="s">
-        <v>141</v>
-      </c>
-      <c r="J115" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" t="s">
-        <v>143</v>
-      </c>
-      <c r="C116">
-        <v>16499</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-      <c r="F116" t="s">
-        <v>117</v>
-      </c>
-      <c r="G116" t="s">
-        <v>137</v>
-      </c>
-      <c r="H116" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" t="s">
-        <v>144</v>
-      </c>
-      <c r="J116" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" t="s">
-        <v>146</v>
-      </c>
-      <c r="C117">
-        <v>16500</v>
-      </c>
-      <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117" t="s">
-        <v>117</v>
-      </c>
-      <c r="G117" t="s">
-        <v>137</v>
-      </c>
-      <c r="H117" t="s">
-        <v>13</v>
-      </c>
-      <c r="I117" t="s">
-        <v>147</v>
-      </c>
-      <c r="J117" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118" t="s">
-        <v>149</v>
-      </c>
-      <c r="C118">
-        <v>16501</v>
-      </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118" t="s">
-        <v>117</v>
-      </c>
-      <c r="G118" t="s">
-        <v>137</v>
-      </c>
-      <c r="H118" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" t="s">
         <v>150</v>
-      </c>
-      <c r="J118" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5733,31 +5602,31 @@
         <v>1000</v>
       </c>
       <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
         <v>152</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>153</v>
       </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>154</v>
-      </c>
-      <c r="J2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5765,7 +5634,7 @@
         <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -5780,16 +5649,16 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J3" t="s">
         <v>157</v>
-      </c>
-      <c r="J3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5797,7 +5666,7 @@
         <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -5812,16 +5681,16 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
       </c>
       <c r="I4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" t="s">
         <v>160</v>
-      </c>
-      <c r="J4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5829,7 +5698,7 @@
         <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -5844,16 +5713,16 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J5" t="s">
         <v>163</v>
-      </c>
-      <c r="J5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5861,7 +5730,7 @@
         <v>1004</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -5876,16 +5745,16 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="I6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6" t="s">
         <v>166</v>
-      </c>
-      <c r="J6" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5893,7 +5762,7 @@
         <v>1005</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5908,16 +5777,16 @@
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="I7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" t="s">
         <v>169</v>
-      </c>
-      <c r="J7" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5925,7 +5794,7 @@
         <v>1006</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -5940,16 +5809,16 @@
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="I8" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" t="s">
         <v>172</v>
-      </c>
-      <c r="J8" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5957,7 +5826,7 @@
         <v>1007</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -5972,16 +5841,16 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
       <c r="I9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J9" t="s">
         <v>175</v>
-      </c>
-      <c r="J9" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5989,7 +5858,7 @@
         <v>1008</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -6004,16 +5873,16 @@
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="I10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J10" t="s">
         <v>178</v>
-      </c>
-      <c r="J10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6021,7 +5890,7 @@
         <v>1009</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -6036,16 +5905,16 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="I11" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" t="s">
         <v>181</v>
-      </c>
-      <c r="J11" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6053,7 +5922,7 @@
         <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -6068,16 +5937,16 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="I12" t="s">
+        <v>183</v>
+      </c>
+      <c r="J12" t="s">
         <v>184</v>
-      </c>
-      <c r="J12" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6085,7 +5954,7 @@
         <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -6100,16 +5969,16 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="I13" t="s">
+        <v>186</v>
+      </c>
+      <c r="J13" t="s">
         <v>187</v>
-      </c>
-      <c r="J13" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6117,31 +5986,31 @@
         <v>1012</v>
       </c>
       <c r="B14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
         <v>189</v>
       </c>
-      <c r="C14">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>190</v>
-      </c>
-      <c r="J14" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6149,7 +6018,7 @@
         <v>1013</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -6164,16 +6033,16 @@
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="I15" t="s">
+        <v>192</v>
+      </c>
+      <c r="J15" t="s">
         <v>193</v>
-      </c>
-      <c r="J15" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6181,7 +6050,7 @@
         <v>1014</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -6196,16 +6065,16 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="I16" t="s">
+        <v>195</v>
+      </c>
+      <c r="J16" t="s">
         <v>196</v>
-      </c>
-      <c r="J16" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6213,7 +6082,7 @@
         <v>1015</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -6228,16 +6097,16 @@
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="I17" t="s">
+        <v>198</v>
+      </c>
+      <c r="J17" t="s">
         <v>199</v>
-      </c>
-      <c r="J17" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6245,7 +6114,7 @@
         <v>1016</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -6260,16 +6129,16 @@
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="I18" t="s">
+        <v>201</v>
+      </c>
+      <c r="J18" t="s">
         <v>202</v>
-      </c>
-      <c r="J18" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6277,7 +6146,7 @@
         <v>1017</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -6292,16 +6161,16 @@
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="I19" t="s">
+        <v>204</v>
+      </c>
+      <c r="J19" t="s">
         <v>205</v>
-      </c>
-      <c r="J19" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6309,7 +6178,7 @@
         <v>1018</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -6324,16 +6193,16 @@
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="I20" t="s">
+        <v>207</v>
+      </c>
+      <c r="J20" t="s">
         <v>208</v>
-      </c>
-      <c r="J20" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6341,7 +6210,7 @@
         <v>1019</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -6356,16 +6225,16 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="I21" t="s">
+        <v>210</v>
+      </c>
+      <c r="J21" t="s">
         <v>211</v>
-      </c>
-      <c r="J21" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6373,7 +6242,7 @@
         <v>1020</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -6388,16 +6257,16 @@
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="I22" t="s">
+        <v>213</v>
+      </c>
+      <c r="J22" t="s">
         <v>214</v>
-      </c>
-      <c r="J22" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6405,7 +6274,7 @@
         <v>1021</v>
       </c>
       <c r="B23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -6420,16 +6289,16 @@
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="I23" t="s">
+        <v>216</v>
+      </c>
+      <c r="J23" t="s">
         <v>217</v>
-      </c>
-      <c r="J23" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6437,7 +6306,7 @@
         <v>1022</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -6452,16 +6321,16 @@
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
       <c r="I24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J24" t="s">
         <v>220</v>
-      </c>
-      <c r="J24" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6469,7 +6338,7 @@
         <v>1023</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -6484,16 +6353,16 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="I25" t="s">
+        <v>222</v>
+      </c>
+      <c r="J25" t="s">
         <v>223</v>
-      </c>
-      <c r="J25" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6501,7 +6370,7 @@
         <v>1024</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -6516,16 +6385,16 @@
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="I26" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" t="s">
         <v>226</v>
-      </c>
-      <c r="J26" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6533,7 +6402,7 @@
         <v>1025</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -6548,16 +6417,16 @@
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
       </c>
       <c r="I27" t="s">
+        <v>228</v>
+      </c>
+      <c r="J27" t="s">
         <v>229</v>
-      </c>
-      <c r="J27" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6565,7 +6434,7 @@
         <v>1026</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -6580,16 +6449,16 @@
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
       </c>
       <c r="I28" t="s">
+        <v>231</v>
+      </c>
+      <c r="J28" t="s">
         <v>232</v>
-      </c>
-      <c r="J28" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6597,7 +6466,7 @@
         <v>1027</v>
       </c>
       <c r="B29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -6612,16 +6481,16 @@
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="I29" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" t="s">
         <v>235</v>
-      </c>
-      <c r="J29" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6629,7 +6498,7 @@
         <v>1028</v>
       </c>
       <c r="B30" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -6644,16 +6513,16 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="I30" t="s">
+        <v>237</v>
+      </c>
+      <c r="J30" t="s">
         <v>238</v>
-      </c>
-      <c r="J30" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -6661,7 +6530,7 @@
         <v>1029</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -6676,16 +6545,16 @@
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
       </c>
       <c r="I31" t="s">
+        <v>240</v>
+      </c>
+      <c r="J31" t="s">
         <v>241</v>
-      </c>
-      <c r="J31" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -6693,7 +6562,7 @@
         <v>1030</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -6708,16 +6577,16 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
       </c>
       <c r="I32" t="s">
+        <v>243</v>
+      </c>
+      <c r="J32" t="s">
         <v>244</v>
-      </c>
-      <c r="J32" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -6725,7 +6594,7 @@
         <v>1031</v>
       </c>
       <c r="B33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -6740,16 +6609,16 @@
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="I33" t="s">
+        <v>246</v>
+      </c>
+      <c r="J33" t="s">
         <v>247</v>
-      </c>
-      <c r="J33" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -6757,7 +6626,7 @@
         <v>1032</v>
       </c>
       <c r="B34" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -6772,16 +6641,16 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="I34" t="s">
+        <v>249</v>
+      </c>
+      <c r="J34" t="s">
         <v>250</v>
-      </c>
-      <c r="J34" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -6789,7 +6658,7 @@
         <v>1033</v>
       </c>
       <c r="B35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -6804,16 +6673,16 @@
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
       </c>
       <c r="I35" t="s">
+        <v>252</v>
+      </c>
+      <c r="J35" t="s">
         <v>253</v>
-      </c>
-      <c r="J35" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -6821,7 +6690,7 @@
         <v>1034</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -6836,16 +6705,16 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="I36" t="s">
+        <v>255</v>
+      </c>
+      <c r="J36" t="s">
         <v>256</v>
-      </c>
-      <c r="J36" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6853,7 +6722,7 @@
         <v>1035</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -6868,16 +6737,16 @@
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="I37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J37" t="s">
         <v>259</v>
-      </c>
-      <c r="J37" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -6885,7 +6754,7 @@
         <v>1036</v>
       </c>
       <c r="B38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -6900,16 +6769,16 @@
         <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
       </c>
       <c r="I38" t="s">
+        <v>261</v>
+      </c>
+      <c r="J38" t="s">
         <v>262</v>
-      </c>
-      <c r="J38" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -6917,7 +6786,7 @@
         <v>1037</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -6932,16 +6801,16 @@
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
       </c>
       <c r="I39" t="s">
+        <v>264</v>
+      </c>
+      <c r="J39" t="s">
         <v>265</v>
-      </c>
-      <c r="J39" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -6949,7 +6818,7 @@
         <v>1038</v>
       </c>
       <c r="B40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -6964,16 +6833,16 @@
         <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="I40" t="s">
+        <v>267</v>
+      </c>
+      <c r="J40" t="s">
         <v>268</v>
-      </c>
-      <c r="J40" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -6981,7 +6850,7 @@
         <v>1039</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -6996,16 +6865,16 @@
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="I41" t="s">
+        <v>270</v>
+      </c>
+      <c r="J41" t="s">
         <v>271</v>
-      </c>
-      <c r="J41" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -7013,7 +6882,7 @@
         <v>1040</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -7028,16 +6897,16 @@
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="I42" t="s">
+        <v>273</v>
+      </c>
+      <c r="J42" t="s">
         <v>274</v>
-      </c>
-      <c r="J42" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -7045,7 +6914,7 @@
         <v>1041</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -7060,16 +6929,16 @@
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="I43" t="s">
+        <v>276</v>
+      </c>
+      <c r="J43" t="s">
         <v>277</v>
-      </c>
-      <c r="J43" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -7077,7 +6946,7 @@
         <v>1042</v>
       </c>
       <c r="B44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -7092,16 +6961,16 @@
         <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="I44" t="s">
+        <v>279</v>
+      </c>
+      <c r="J44" t="s">
         <v>280</v>
-      </c>
-      <c r="J44" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -7109,7 +6978,7 @@
         <v>1043</v>
       </c>
       <c r="B45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -7124,16 +6993,16 @@
         <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="I45" t="s">
+        <v>282</v>
+      </c>
+      <c r="J45" t="s">
         <v>283</v>
-      </c>
-      <c r="J45" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -7190,7 +7059,7 @@
         <v>3000</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2">
         <v>24577</v>
@@ -7205,16 +7074,16 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
       <c r="I2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J2" t="s">
         <v>286</v>
-      </c>
-      <c r="J2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7222,7 +7091,7 @@
         <v>3001</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>24578</v>
@@ -7237,16 +7106,16 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J3" t="s">
         <v>289</v>
-      </c>
-      <c r="J3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7254,7 +7123,7 @@
         <v>3002</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C4">
         <v>24579</v>
@@ -7269,16 +7138,16 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
       </c>
       <c r="I4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J4" t="s">
         <v>292</v>
-      </c>
-      <c r="J4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7286,7 +7155,7 @@
         <v>3003</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5">
         <v>24580</v>
@@ -7301,16 +7170,16 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5" t="s">
+        <v>294</v>
+      </c>
+      <c r="J5" t="s">
         <v>295</v>
-      </c>
-      <c r="J5" t="s">
-        <v>296</v>
       </c>
     </row>
   </sheetData>
